--- a/SGP/SGP-ID-Bulletins.xlsx
+++ b/SGP/SGP-ID-Bulletins.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t>source_file_name</t>
   </si>
@@ -43,139 +43,187 @@
     <t>ARI_samples_COVID_19_pct</t>
   </si>
   <si>
-    <t>Weekly ID Bulletin - E-week 1.pdf</t>
-  </si>
-  <si>
-    <t>Weekly ID Bulletin - E-week 2.pdf</t>
-  </si>
-  <si>
-    <t>Weekly ID Bulletin - E-week 3.pdf</t>
-  </si>
-  <si>
-    <t>Weekly ID Bulletin E-Week 4.pdf</t>
-  </si>
-  <si>
-    <t>Weekly ID Bulletin E-week 5_2.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW6-2025_final.pdf</t>
-  </si>
-  <si>
-    <t>Weekly ID bulletin E-week 7.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW8-2025_final.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 9.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 10.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 11.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 12.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 13.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 14.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 15.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 16.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 17.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 18.pdf</t>
-  </si>
-  <si>
-    <t>2025_week_19.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 20.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 21.pdf</t>
-  </si>
-  <si>
-    <t>2025_week_22.pdf</t>
-  </si>
-  <si>
-    <t>2025_week_23.pdf</t>
-  </si>
-  <si>
-    <t>2025_week_24.pdf</t>
-  </si>
-  <si>
-    <t>2025_week_25.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 26.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 27.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 28.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 29.pdf</t>
-  </si>
-  <si>
-    <t>WIDB_EW30-2025.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 31.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW32.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 33.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 34.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 35.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 36.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 37.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 38.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 39.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 40.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 41.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 42.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 44.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 45.pdf</t>
-  </si>
-  <si>
-    <t>Weekly Infectious Disease Bulletin EW 46.pdf</t>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\2025_week_19.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\2025_week_22.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\2025_week_23.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\2025_week_24.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\2025_week_25.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly ID Bulletin - E-week 1.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly ID Bulletin - E-week 2.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly ID Bulletin - E-week 3.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly ID Bulletin E-Week 4.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly ID Bulletin E-week 5_2.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly ID bulletin E-week 7.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 10.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 11.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 12.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 13.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 14.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 15.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 16.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 17.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 18.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 20.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 21.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 26.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 27.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 28.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 29.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 31.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 33.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 34.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 35.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 36.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 37.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 38.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 39.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 40.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 41.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 42.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 44.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 45.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 46.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 47.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 48.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 49.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 50.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 51.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 52.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 53.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW 9.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW32.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW6-2025_final.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\Weekly Infectious Disease Bulletin EW8-2025_final.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2025\WIDB_EW30-2025.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 1.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 2.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 3.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 4.pdf</t>
+  </si>
+  <si>
+    <t>4 - 10 May 2025</t>
+  </si>
+  <si>
+    <t>25 - 31 May 2025</t>
+  </si>
+  <si>
+    <t>1 - 7 Jun 2025</t>
+  </si>
+  <si>
+    <t>8 - 14 Jun 2025</t>
+  </si>
+  <si>
+    <t>15 - 21 Jun 2025</t>
   </si>
   <si>
     <t>29 Dec 2024 - 4 Jan 2025</t>
@@ -193,124 +241,157 @@
     <t>26 Jan 2025 - 1 Feb 2025</t>
   </si>
   <si>
+    <t>9 - 15 Feb 2025</t>
+  </si>
+  <si>
+    <t>2 - 8 Mar 2025</t>
+  </si>
+  <si>
+    <t>9 - 15 Mar 2025</t>
+  </si>
+  <si>
+    <t>16 - 22 Mar 2025</t>
+  </si>
+  <si>
+    <t>23 - 29 Mar 2025</t>
+  </si>
+  <si>
+    <t>30 Mar 2024 - 5 Apr 2025</t>
+  </si>
+  <si>
+    <t>6 - 12 Apr 2025</t>
+  </si>
+  <si>
+    <t>13 - 19 Apr 2025</t>
+  </si>
+  <si>
+    <t>20 - 26 Apr 2025</t>
+  </si>
+  <si>
+    <t>27 Apr - 3 May 2025</t>
+  </si>
+  <si>
+    <t>11 - 17 May 2025</t>
+  </si>
+  <si>
+    <t>18 - 24 May 2025</t>
+  </si>
+  <si>
+    <t>22 - 28 Jun 2025</t>
+  </si>
+  <si>
+    <t>29 Jun 2024 - 5 Jul 2025</t>
+  </si>
+  <si>
+    <t>6 - 12 Jul 2025</t>
+  </si>
+  <si>
+    <t>13 - 19 Jul 2025</t>
+  </si>
+  <si>
+    <t>27 Jul 2024 - 2 Aug 2025</t>
+  </si>
+  <si>
+    <t>10 - 16 Aug 2025</t>
+  </si>
+  <si>
+    <t>17 - 23 Aug 2025</t>
+  </si>
+  <si>
+    <t>24 - 30 Aug 2025</t>
+  </si>
+  <si>
+    <t>31 Aug 2024 - 6 Sep 2025</t>
+  </si>
+  <si>
+    <t>7 - 13 Sep 2025</t>
+  </si>
+  <si>
+    <t>14 - 20 Sep 2025</t>
+  </si>
+  <si>
+    <t>21 - 27 Sep 2025</t>
+  </si>
+  <si>
+    <t>28 Sep 2024 - 4 Oct 2025</t>
+  </si>
+  <si>
+    <t>5 - 11 Oct 2025</t>
+  </si>
+  <si>
+    <t>12 - 18 Oct 2025</t>
+  </si>
+  <si>
+    <t>26 Oct 2025 - 1 Nov 2025</t>
+  </si>
+  <si>
+    <t>2 - 8 Nov 2025</t>
+  </si>
+  <si>
+    <t>9 - 15 Nov 2025</t>
+  </si>
+  <si>
+    <t>16 - 22 Nov 2025</t>
+  </si>
+  <si>
+    <t>23 - 29 Nov 2025</t>
+  </si>
+  <si>
+    <t>30 Nov 2025 - 6 Dec 2025</t>
+  </si>
+  <si>
+    <t>7 - 13 Dec 2025</t>
+  </si>
+  <si>
+    <t>14 - 20 Dec 2025</t>
+  </si>
+  <si>
+    <t>21 - 27 Dec 2025</t>
+  </si>
+  <si>
+    <t>28 Dec 2025 - 3 Jan 2025</t>
+  </si>
+  <si>
+    <t>23 Feb 2024 - 1 Mar 2025</t>
+  </si>
+  <si>
+    <t>3 - 9 Aug 2025</t>
+  </si>
+  <si>
     <t>2 - 8 Feb 2025</t>
   </si>
   <si>
-    <t>9 - 15 Feb 2025</t>
-  </si>
-  <si>
     <t>16 - 22 Feb 2025</t>
   </si>
   <si>
-    <t>23 Feb 2024 - 1 Mar 2025</t>
-  </si>
-  <si>
-    <t>2 - 8 Mar 2025</t>
-  </si>
-  <si>
-    <t>9 - 15 Mar 2025</t>
-  </si>
-  <si>
-    <t>16 - 22 Mar 2025</t>
-  </si>
-  <si>
-    <t>23 - 29 Mar 2025</t>
-  </si>
-  <si>
-    <t>30 Mar 2024 - 5 Apr 2025</t>
-  </si>
-  <si>
-    <t>6 - 12 Apr 2025</t>
-  </si>
-  <si>
-    <t>13 - 19 Apr 2025</t>
-  </si>
-  <si>
-    <t>20 - 26 Apr 2025</t>
-  </si>
-  <si>
-    <t>27 Apr - 3 May 2025</t>
-  </si>
-  <si>
-    <t>4 - 10 May 2025</t>
-  </si>
-  <si>
-    <t>11 - 17 May 2025</t>
-  </si>
-  <si>
-    <t>18 - 24 May 2025</t>
-  </si>
-  <si>
-    <t>25 - 31 May 2025</t>
-  </si>
-  <si>
-    <t>1 - 7 Jun 2025</t>
-  </si>
-  <si>
-    <t>8 - 14 Jun 2025</t>
-  </si>
-  <si>
-    <t>15 - 21 Jun 2025</t>
-  </si>
-  <si>
-    <t>22 - 28 Jun 2025</t>
-  </si>
-  <si>
-    <t>29 Jun 2024 - 5 Jul 2025</t>
-  </si>
-  <si>
-    <t>6 - 12 Jul 2025</t>
-  </si>
-  <si>
-    <t>13 - 19 Jul 2025</t>
-  </si>
-  <si>
     <t>20 - 26 Jul 2025</t>
   </si>
   <si>
-    <t>27 Jul 2024 - 2 Aug 2025</t>
-  </si>
-  <si>
-    <t>3 - 9 Aug 2025</t>
-  </si>
-  <si>
-    <t>10 - 16 Aug 2025</t>
-  </si>
-  <si>
-    <t>17 - 23 Aug 2025</t>
-  </si>
-  <si>
-    <t>24 - 30 Aug 2025</t>
-  </si>
-  <si>
-    <t>31 Aug 2024 - 6 Sep 2025</t>
-  </si>
-  <si>
-    <t>7 - 13 Sep 2025</t>
-  </si>
-  <si>
-    <t>14 - 20 Sep 2025</t>
-  </si>
-  <si>
-    <t>21 - 27 Sep 2025</t>
-  </si>
-  <si>
-    <t>28 Sep 2024 - 4 Oct 2025</t>
-  </si>
-  <si>
-    <t>5 - 11 Oct 2025</t>
-  </si>
-  <si>
-    <t>12 - 18 Oct 2025</t>
-  </si>
-  <si>
-    <t>26 Oct 2025 - 1 Nov 2025</t>
-  </si>
-  <si>
-    <t>2 - 8 Nov 2025</t>
-  </si>
-  <si>
-    <t>9 - 15 Nov 2025</t>
+    <t>4 - 10 Jan 2026</t>
+  </si>
+  <si>
+    <t>11 - 17 Jan 2026</t>
+  </si>
+  <si>
+    <t>18 - 24 Jan 2026</t>
+  </si>
+  <si>
+    <t>25 - 31 Jan 2026</t>
+  </si>
+  <si>
+    <t>10 May 2025</t>
+  </si>
+  <si>
+    <t>31 May 2025</t>
+  </si>
+  <si>
+    <t>7 Jun 2025</t>
+  </si>
+  <si>
+    <t>14 Jun 2025</t>
+  </si>
+  <si>
+    <t>21 Jun 2025</t>
   </si>
   <si>
     <t>4 Jan 2025</t>
@@ -328,124 +409,142 @@
     <t>1 Feb 2025</t>
   </si>
   <si>
+    <t>15 Feb 2025</t>
+  </si>
+  <si>
+    <t>8 Mar 2025</t>
+  </si>
+  <si>
+    <t>15 Mar 2025</t>
+  </si>
+  <si>
+    <t>22 Mar 2025</t>
+  </si>
+  <si>
+    <t>29 Mar 2025</t>
+  </si>
+  <si>
+    <t>5 Apr 2025</t>
+  </si>
+  <si>
+    <t>12 Apr 2025</t>
+  </si>
+  <si>
+    <t>19 Apr 2025</t>
+  </si>
+  <si>
+    <t>26 Apr 2025</t>
+  </si>
+  <si>
+    <t>3 May 2025</t>
+  </si>
+  <si>
+    <t>17 May 2025</t>
+  </si>
+  <si>
+    <t>24 May 2025</t>
+  </si>
+  <si>
+    <t>28 Jun 2025</t>
+  </si>
+  <si>
+    <t>5 Jul 2025</t>
+  </si>
+  <si>
+    <t>12 Jul 2025</t>
+  </si>
+  <si>
+    <t>19 Jul 2025</t>
+  </si>
+  <si>
+    <t>2 Aug 2025</t>
+  </si>
+  <si>
+    <t>16 Aug 2025</t>
+  </si>
+  <si>
+    <t>23 Aug 2025</t>
+  </si>
+  <si>
+    <t>30 Aug 2025</t>
+  </si>
+  <si>
+    <t>6 Sep 2025</t>
+  </si>
+  <si>
+    <t>13 Sep 2025</t>
+  </si>
+  <si>
+    <t>20 Sep 2025</t>
+  </si>
+  <si>
+    <t>27 Sep 2025</t>
+  </si>
+  <si>
+    <t>4 Oct 2025</t>
+  </si>
+  <si>
+    <t>11 Oct 2025</t>
+  </si>
+  <si>
+    <t>18 Oct 2025</t>
+  </si>
+  <si>
+    <t>1 Nov 2025</t>
+  </si>
+  <si>
+    <t>8 Nov 2025</t>
+  </si>
+  <si>
+    <t>15 Nov 2025</t>
+  </si>
+  <si>
+    <t>22 Nov 2025</t>
+  </si>
+  <si>
+    <t>29 Nov 2025</t>
+  </si>
+  <si>
+    <t>6 Dec 2025</t>
+  </si>
+  <si>
+    <t>13 Dec 2025</t>
+  </si>
+  <si>
+    <t>20 Dec 2025</t>
+  </si>
+  <si>
+    <t>27 Dec 2025</t>
+  </si>
+  <si>
+    <t>3 Jan 2025</t>
+  </si>
+  <si>
+    <t>1 Mar 2025</t>
+  </si>
+  <si>
+    <t>9 Aug 2025</t>
+  </si>
+  <si>
     <t>8 Feb 2025</t>
   </si>
   <si>
-    <t>15 Feb 2025</t>
-  </si>
-  <si>
     <t>22 Feb 2025</t>
   </si>
   <si>
-    <t>1 Mar 2025</t>
-  </si>
-  <si>
-    <t>8 Mar 2025</t>
-  </si>
-  <si>
-    <t>15 Mar 2025</t>
-  </si>
-  <si>
-    <t>22 Mar 2025</t>
-  </si>
-  <si>
-    <t>29 Mar 2025</t>
-  </si>
-  <si>
-    <t>5 Apr 2025</t>
-  </si>
-  <si>
-    <t>12 Apr 2025</t>
-  </si>
-  <si>
-    <t>19 Apr 2025</t>
-  </si>
-  <si>
-    <t>26 Apr 2025</t>
-  </si>
-  <si>
-    <t>3 May 2025</t>
-  </si>
-  <si>
-    <t>10 May 2025</t>
-  </si>
-  <si>
-    <t>17 May 2025</t>
-  </si>
-  <si>
-    <t>24 May 2025</t>
-  </si>
-  <si>
-    <t>31 May 2025</t>
-  </si>
-  <si>
-    <t>7 Jun 2025</t>
-  </si>
-  <si>
-    <t>14 Jun 2025</t>
-  </si>
-  <si>
-    <t>21 Jun 2025</t>
-  </si>
-  <si>
-    <t>28 Jun 2025</t>
-  </si>
-  <si>
-    <t>5 Jul 2025</t>
-  </si>
-  <si>
-    <t>12 Jul 2025</t>
-  </si>
-  <si>
-    <t>19 Jul 2025</t>
-  </si>
-  <si>
     <t>26 Jul 2025</t>
   </si>
   <si>
-    <t>2 Aug 2025</t>
-  </si>
-  <si>
-    <t>9 Aug 2025</t>
-  </si>
-  <si>
-    <t>16 Aug 2025</t>
-  </si>
-  <si>
-    <t>23 Aug 2025</t>
-  </si>
-  <si>
-    <t>30 Aug 2025</t>
-  </si>
-  <si>
-    <t>6 Sep 2025</t>
-  </si>
-  <si>
-    <t>13 Sep 2025</t>
-  </si>
-  <si>
-    <t>20 Sep 2025</t>
-  </si>
-  <si>
-    <t>27 Sep 2025</t>
-  </si>
-  <si>
-    <t>4 Oct 2025</t>
-  </si>
-  <si>
-    <t>11 Oct 2025</t>
-  </si>
-  <si>
-    <t>18 Oct 2025</t>
-  </si>
-  <si>
-    <t>1 Nov 2025</t>
-  </si>
-  <si>
-    <t>8 Nov 2025</t>
-  </si>
-  <si>
-    <t>15 Nov 2025</t>
+    <t>10 Jan 2026</t>
+  </si>
+  <si>
+    <t>17 Jan 2026</t>
+  </si>
+  <si>
+    <t>24 Jan 2026</t>
+  </si>
+  <si>
+    <t>31 Jan 2026</t>
   </si>
 </sst>
 </file>
@@ -803,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -843,28 +942,28 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2711</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>170</v>
+        <v>319</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -875,28 +974,28 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>2714</v>
+        <v>2636</v>
       </c>
       <c r="G3">
         <v>9</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>502</v>
+        <v>370</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -907,28 +1006,28 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>2866</v>
+        <v>2338</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>417</v>
+        <v>341</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -939,28 +1038,28 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="F5">
-        <v>3045</v>
+        <v>2154</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>484</v>
+        <v>308</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -971,28 +1070,28 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="F6">
-        <v>3392</v>
+        <v>1996</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1003,16 +1102,16 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="F7">
-        <v>3381</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1021,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>508</v>
+        <v>170</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1035,28 +1134,28 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F8">
-        <v>3046</v>
+        <v>2714</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1067,28 +1166,28 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="F9">
-        <v>2749</v>
+        <v>2866</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1099,16 +1198,16 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="F10">
-        <v>2617</v>
+        <v>3045</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1117,10 +1216,10 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>361</v>
+        <v>484</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1131,16 +1230,16 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="F11">
-        <v>2542</v>
+        <v>3392</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1149,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>365</v>
+        <v>260</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -1163,16 +1262,16 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="F12">
-        <v>2431</v>
+        <v>3046</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1181,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>365</v>
+        <v>524</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1195,16 +1294,16 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="F13">
-        <v>2179</v>
+        <v>2542</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1213,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1227,28 +1326,28 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="F14">
-        <v>2424</v>
+        <v>2431</v>
       </c>
       <c r="G14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1259,28 +1358,28 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="F15">
-        <v>2471</v>
+        <v>2179</v>
       </c>
       <c r="G15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="J15">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1291,28 +1390,28 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="F16">
-        <v>2632</v>
+        <v>2424</v>
       </c>
       <c r="G16">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="J16">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1323,28 +1422,28 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="F17">
-        <v>2749</v>
+        <v>2471</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="J17">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1355,28 +1454,28 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="F18">
-        <v>2781</v>
+        <v>2632</v>
       </c>
       <c r="G18">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="J18">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1387,28 +1486,28 @@
         <v>26</v>
       </c>
       <c r="C19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="F19">
-        <v>2906</v>
+        <v>2749</v>
       </c>
       <c r="G19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="J19">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1419,28 +1518,28 @@
         <v>27</v>
       </c>
       <c r="C20">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="F20">
-        <v>2711</v>
+        <v>2781</v>
       </c>
       <c r="G20">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="J20">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1451,28 +1550,28 @@
         <v>28</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F21">
-        <v>2828</v>
+        <v>2906</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>316</v>
+        <v>269</v>
       </c>
       <c r="J21">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1483,28 +1582,28 @@
         <v>29</v>
       </c>
       <c r="C22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="F22">
-        <v>2856</v>
+        <v>2828</v>
       </c>
       <c r="G22">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H22">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>399</v>
+        <v>316</v>
       </c>
       <c r="J22">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1515,28 +1614,28 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="F23">
-        <v>2636</v>
+        <v>2856</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H23">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I23">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="J23">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1547,28 +1646,28 @@
         <v>31</v>
       </c>
       <c r="C24">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="F24">
-        <v>2338</v>
+        <v>2018</v>
       </c>
       <c r="G24">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="J24">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1579,28 +1678,28 @@
         <v>32</v>
       </c>
       <c r="C25">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="F25">
-        <v>2154</v>
+        <v>2147</v>
       </c>
       <c r="G25">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="J25">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1611,25 +1710,25 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="F26">
-        <v>1996</v>
+        <v>2148</v>
       </c>
       <c r="G26">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>305</v>
+        <v>246</v>
       </c>
       <c r="J26">
         <v>16</v>
@@ -1643,28 +1742,28 @@
         <v>34</v>
       </c>
       <c r="C27">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="F27">
-        <v>2018</v>
+        <v>2282</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H27">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="J27">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1675,28 +1774,28 @@
         <v>35</v>
       </c>
       <c r="C28">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="F28">
-        <v>2147</v>
+        <v>2298</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="J28">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1707,28 +1806,28 @@
         <v>36</v>
       </c>
       <c r="C29">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="F29">
-        <v>2148</v>
+        <v>2353</v>
       </c>
       <c r="G29">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>246</v>
+        <v>289</v>
       </c>
       <c r="J29">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1739,28 +1838,28 @@
         <v>37</v>
       </c>
       <c r="C30">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="F30">
-        <v>2282</v>
+        <v>2501</v>
       </c>
       <c r="G30">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>251</v>
+        <v>314</v>
       </c>
       <c r="J30">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1771,28 +1870,28 @@
         <v>38</v>
       </c>
       <c r="C31">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="F31">
-        <v>2304</v>
+        <v>2553</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="J31">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1803,16 +1902,16 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="F32">
-        <v>2298</v>
+        <v>2520</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1821,10 +1920,10 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1835,28 +1934,28 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F33">
-        <v>2274</v>
+        <v>2498</v>
       </c>
       <c r="G33">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1867,28 +1966,28 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="F34">
-        <v>2353</v>
+        <v>2809</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>289</v>
+        <v>360</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1899,16 +1998,16 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E35" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="F35">
-        <v>2501</v>
+        <v>2748</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1917,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>314</v>
+        <v>439</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1931,16 +2030,16 @@
         <v>43</v>
       </c>
       <c r="C36">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E36" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="F36">
-        <v>2553</v>
+        <v>2646</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -1949,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>283</v>
+        <v>366</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1963,16 +2062,16 @@
         <v>44</v>
       </c>
       <c r="C37">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="F37">
-        <v>2520</v>
+        <v>2715</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -1981,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>307</v>
+        <v>381</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1995,16 +2094,16 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E38" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="F38">
-        <v>2498</v>
+        <v>2776</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -2013,10 +2112,10 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>321</v>
+        <v>374</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2027,16 +2126,16 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E39" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="F39">
-        <v>2809</v>
+        <v>2592</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2045,10 +2144,10 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2059,16 +2158,16 @@
         <v>47</v>
       </c>
       <c r="C40">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E40" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="F40">
-        <v>2748</v>
+        <v>2487</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -2077,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>439</v>
+        <v>316</v>
       </c>
       <c r="J40">
         <v>2</v>
@@ -2091,16 +2190,16 @@
         <v>48</v>
       </c>
       <c r="C41">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E41" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="F41">
-        <v>2646</v>
+        <v>2445</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2109,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2123,16 +2222,16 @@
         <v>49</v>
       </c>
       <c r="C42">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="F42">
-        <v>2715</v>
+        <v>2443</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -2141,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2155,16 +2254,16 @@
         <v>50</v>
       </c>
       <c r="C43">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="F43">
-        <v>2776</v>
+        <v>2450</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2173,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2187,16 +2286,16 @@
         <v>51</v>
       </c>
       <c r="C44">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E44" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="F44">
-        <v>2592</v>
+        <v>2452</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -2205,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="J44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2219,16 +2318,16 @@
         <v>52</v>
       </c>
       <c r="C45">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E45" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="F45">
-        <v>2487</v>
+        <v>2523</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2237,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2251,27 +2350,379 @@
         <v>53</v>
       </c>
       <c r="C46">
+        <v>51</v>
+      </c>
+      <c r="D46" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46">
+        <v>2452</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>280</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47">
+        <v>52</v>
+      </c>
+      <c r="D47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" t="s">
+        <v>166</v>
+      </c>
+      <c r="F47">
+        <v>2735</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>159</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="D46" t="s">
-        <v>98</v>
-      </c>
-      <c r="E46" t="s">
-        <v>143</v>
-      </c>
-      <c r="F46">
-        <v>2445</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
+      <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48">
+        <v>53</v>
+      </c>
+      <c r="D48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" t="s">
+        <v>167</v>
+      </c>
+      <c r="F48">
+        <v>2832</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>194</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49">
+        <v>9</v>
+      </c>
+      <c r="D49" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" t="s">
+        <v>168</v>
+      </c>
+      <c r="F49">
+        <v>2617</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>361</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50">
+        <v>32</v>
+      </c>
+      <c r="D50" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" t="s">
+        <v>169</v>
+      </c>
+      <c r="F50">
+        <v>2274</v>
+      </c>
+      <c r="G50">
+        <v>9</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>276</v>
+      </c>
+      <c r="J50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" t="s">
+        <v>170</v>
+      </c>
+      <c r="F51">
+        <v>3381</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>508</v>
+      </c>
+      <c r="J51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" t="s">
+        <v>171</v>
+      </c>
+      <c r="F52">
+        <v>2749</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>416</v>
+      </c>
+      <c r="J52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53">
+        <v>30</v>
+      </c>
+      <c r="D53" t="s">
+        <v>116</v>
+      </c>
+      <c r="E53" t="s">
+        <v>172</v>
+      </c>
+      <c r="F53">
+        <v>2304</v>
+      </c>
+      <c r="G53">
+        <v>9</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>243</v>
+      </c>
+      <c r="J53">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>117</v>
+      </c>
+      <c r="E54" t="s">
+        <v>173</v>
+      </c>
+      <c r="F54">
+        <v>2857</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>344</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55" t="s">
+        <v>174</v>
+      </c>
+      <c r="F55">
+        <v>2938</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>260</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56" t="s">
+        <v>175</v>
+      </c>
+      <c r="F56">
+        <v>3093</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>281</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" t="s">
+        <v>176</v>
+      </c>
+      <c r="F57">
+        <v>3017</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
         <v>0</v>
       </c>
     </row>

--- a/SGP/SGP-ID-Bulletins.xlsx
+++ b/SGP/SGP-ID-Bulletins.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t>source_file_name</t>
   </si>
@@ -211,6 +211,9 @@
     <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 4.pdf</t>
   </si>
   <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 5.pdf</t>
+  </si>
+  <si>
     <t>4 - 10 May 2025</t>
   </si>
   <si>
@@ -379,6 +382,9 @@
     <t>25 - 31 Jan 2026</t>
   </si>
   <si>
+    <t>1 - 7 Feb 2026</t>
+  </si>
+  <si>
     <t>10 May 2025</t>
   </si>
   <si>
@@ -545,6 +551,9 @@
   </si>
   <si>
     <t>31 Jan 2026</t>
+  </si>
+  <si>
+    <t>7 Feb 2026</t>
   </si>
 </sst>
 </file>
@@ -902,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -945,10 +954,10 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F2">
         <v>2711</v>
@@ -977,10 +986,10 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F3">
         <v>2636</v>
@@ -1009,10 +1018,10 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F4">
         <v>2338</v>
@@ -1041,10 +1050,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F5">
         <v>2154</v>
@@ -1073,10 +1082,10 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F6">
         <v>1996</v>
@@ -1105,10 +1114,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1137,10 +1146,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F8">
         <v>2714</v>
@@ -1169,10 +1178,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F9">
         <v>2866</v>
@@ -1201,10 +1210,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F10">
         <v>3045</v>
@@ -1233,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F11">
         <v>3392</v>
@@ -1265,10 +1274,10 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F12">
         <v>3046</v>
@@ -1297,10 +1306,10 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F13">
         <v>2542</v>
@@ -1329,10 +1338,10 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F14">
         <v>2431</v>
@@ -1361,10 +1370,10 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F15">
         <v>2179</v>
@@ -1393,10 +1402,10 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F16">
         <v>2424</v>
@@ -1425,10 +1434,10 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F17">
         <v>2471</v>
@@ -1457,10 +1466,10 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F18">
         <v>2632</v>
@@ -1489,10 +1498,10 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F19">
         <v>2749</v>
@@ -1521,10 +1530,10 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F20">
         <v>2781</v>
@@ -1553,10 +1562,10 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F21">
         <v>2906</v>
@@ -1585,10 +1594,10 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F22">
         <v>2828</v>
@@ -1617,10 +1626,10 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F23">
         <v>2856</v>
@@ -1649,10 +1658,10 @@
         <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F24">
         <v>2018</v>
@@ -1681,10 +1690,10 @@
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F25">
         <v>2147</v>
@@ -1713,10 +1722,10 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F26">
         <v>2148</v>
@@ -1745,10 +1754,10 @@
         <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F27">
         <v>2282</v>
@@ -1777,10 +1786,10 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F28">
         <v>2298</v>
@@ -1809,10 +1818,10 @@
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F29">
         <v>2353</v>
@@ -1841,10 +1850,10 @@
         <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F30">
         <v>2501</v>
@@ -1873,10 +1882,10 @@
         <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F31">
         <v>2553</v>
@@ -1905,10 +1914,10 @@
         <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F32">
         <v>2520</v>
@@ -1937,10 +1946,10 @@
         <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F33">
         <v>2498</v>
@@ -1969,10 +1978,10 @@
         <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F34">
         <v>2809</v>
@@ -2001,10 +2010,10 @@
         <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F35">
         <v>2748</v>
@@ -2033,10 +2042,10 @@
         <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E36" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F36">
         <v>2646</v>
@@ -2065,10 +2074,10 @@
         <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E37" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F37">
         <v>2715</v>
@@ -2097,10 +2106,10 @@
         <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F38">
         <v>2776</v>
@@ -2129,10 +2138,10 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E39" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F39">
         <v>2592</v>
@@ -2161,10 +2170,10 @@
         <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F40">
         <v>2487</v>
@@ -2193,10 +2202,10 @@
         <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E41" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F41">
         <v>2445</v>
@@ -2225,10 +2234,10 @@
         <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F42">
         <v>2443</v>
@@ -2257,10 +2266,10 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E43" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F43">
         <v>2450</v>
@@ -2289,10 +2298,10 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E44" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F44">
         <v>2452</v>
@@ -2321,10 +2330,10 @@
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E45" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F45">
         <v>2523</v>
@@ -2353,10 +2362,10 @@
         <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E46" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F46">
         <v>2452</v>
@@ -2385,10 +2394,10 @@
         <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E47" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F47">
         <v>2735</v>
@@ -2417,10 +2426,10 @@
         <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F48">
         <v>2832</v>
@@ -2449,10 +2458,10 @@
         <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F49">
         <v>2617</v>
@@ -2481,10 +2490,10 @@
         <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F50">
         <v>2274</v>
@@ -2513,10 +2522,10 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E51" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F51">
         <v>3381</v>
@@ -2545,10 +2554,10 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F52">
         <v>2749</v>
@@ -2577,10 +2586,10 @@
         <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F53">
         <v>2304</v>
@@ -2609,10 +2618,10 @@
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F54">
         <v>2857</v>
@@ -2641,10 +2650,10 @@
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F55">
         <v>2938</v>
@@ -2673,10 +2682,10 @@
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E56" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F56">
         <v>3093</v>
@@ -2705,10 +2714,10 @@
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E57" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F57">
         <v>3017</v>
@@ -2723,6 +2732,38 @@
         <v>0</v>
       </c>
       <c r="J57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" t="s">
+        <v>179</v>
+      </c>
+      <c r="F58">
+        <v>2992</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
         <v>0</v>
       </c>
     </row>

--- a/SGP/SGP-ID-Bulletins.xlsx
+++ b/SGP/SGP-ID-Bulletins.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
   <si>
     <t>source_file_name</t>
   </si>
@@ -202,6 +202,27 @@
     <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 1.pdf</t>
   </si>
   <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 10.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 11.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 12.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 13.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 14.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 15.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 16.pdf</t>
+  </si>
+  <si>
     <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 2.pdf</t>
   </si>
   <si>
@@ -214,6 +235,18 @@
     <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 5.pdf</t>
   </si>
   <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 6.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 7.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 8.pdf</t>
+  </si>
+  <si>
+    <t>c:/dev/covid-19-world-vaccinations/SGP/2026\Weekly Infectious Disease Bulletin EW 9.pdf</t>
+  </si>
+  <si>
     <t>4 - 10 May 2025</t>
   </si>
   <si>
@@ -373,6 +406,27 @@
     <t>4 - 10 Jan 2026</t>
   </si>
   <si>
+    <t>8 - 14 Mar 2026</t>
+  </si>
+  <si>
+    <t>15 - 21 Mar 2026</t>
+  </si>
+  <si>
+    <t>22 - 28 Mar 2026</t>
+  </si>
+  <si>
+    <t>29 Mar 2025 - 4 Apr 2026</t>
+  </si>
+  <si>
+    <t>5 - 11 Apr 2026</t>
+  </si>
+  <si>
+    <t>12 - 18 Apr 2026</t>
+  </si>
+  <si>
+    <t>19 - 25 Apr 2026</t>
+  </si>
+  <si>
     <t>11 - 17 Jan 2026</t>
   </si>
   <si>
@@ -385,6 +439,18 @@
     <t>1 - 7 Feb 2026</t>
   </si>
   <si>
+    <t>8 - 14 Feb 2026</t>
+  </si>
+  <si>
+    <t>15 - 21 Feb 2026</t>
+  </si>
+  <si>
+    <t>22 - 28 Feb 2026</t>
+  </si>
+  <si>
+    <t>1 - 7 Mar 2026</t>
+  </si>
+  <si>
     <t>10 May 2025</t>
   </si>
   <si>
@@ -544,6 +610,27 @@
     <t>10 Jan 2026</t>
   </si>
   <si>
+    <t>14 Mar 2026</t>
+  </si>
+  <si>
+    <t>21 Mar 2026</t>
+  </si>
+  <si>
+    <t>28 Mar 2026</t>
+  </si>
+  <si>
+    <t>4 Apr 2026</t>
+  </si>
+  <si>
+    <t>11 Apr 2026</t>
+  </si>
+  <si>
+    <t>18 Apr 2026</t>
+  </si>
+  <si>
+    <t>25 Apr 2026</t>
+  </si>
+  <si>
     <t>17 Jan 2026</t>
   </si>
   <si>
@@ -554,6 +641,18 @@
   </si>
   <si>
     <t>7 Feb 2026</t>
+  </si>
+  <si>
+    <t>14 Feb 2026</t>
+  </si>
+  <si>
+    <t>21 Feb 2026</t>
+  </si>
+  <si>
+    <t>28 Feb 2026</t>
+  </si>
+  <si>
+    <t>7 Mar 2026</t>
   </si>
 </sst>
 </file>
@@ -911,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -954,10 +1053,10 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="F2">
         <v>2711</v>
@@ -986,10 +1085,10 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>2636</v>
@@ -1018,10 +1117,10 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="F4">
         <v>2338</v>
@@ -1050,10 +1149,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="F5">
         <v>2154</v>
@@ -1082,10 +1181,10 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="F6">
         <v>1996</v>
@@ -1114,10 +1213,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1146,10 +1245,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="F8">
         <v>2714</v>
@@ -1178,10 +1277,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F9">
         <v>2866</v>
@@ -1210,10 +1309,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="F10">
         <v>3045</v>
@@ -1242,10 +1341,10 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="F11">
         <v>3392</v>
@@ -1274,10 +1373,10 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="F12">
         <v>3046</v>
@@ -1306,10 +1405,10 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="F13">
         <v>2542</v>
@@ -1338,10 +1437,10 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="F14">
         <v>2431</v>
@@ -1370,10 +1469,10 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="F15">
         <v>2179</v>
@@ -1402,10 +1501,10 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="F16">
         <v>2424</v>
@@ -1434,10 +1533,10 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="F17">
         <v>2471</v>
@@ -1466,10 +1565,10 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="F18">
         <v>2632</v>
@@ -1498,10 +1597,10 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="F19">
         <v>2749</v>
@@ -1530,10 +1629,10 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="F20">
         <v>2781</v>
@@ -1562,10 +1661,10 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="F21">
         <v>2906</v>
@@ -1594,10 +1693,10 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="F22">
         <v>2828</v>
@@ -1626,10 +1725,10 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="F23">
         <v>2856</v>
@@ -1658,10 +1757,10 @@
         <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="F24">
         <v>2018</v>
@@ -1690,10 +1789,10 @@
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="F25">
         <v>2147</v>
@@ -1722,10 +1821,10 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="F26">
         <v>2148</v>
@@ -1754,10 +1853,10 @@
         <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F27">
         <v>2282</v>
@@ -1786,10 +1885,10 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="F28">
         <v>2298</v>
@@ -1818,10 +1917,10 @@
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="F29">
         <v>2353</v>
@@ -1850,10 +1949,10 @@
         <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="F30">
         <v>2501</v>
@@ -1882,10 +1981,10 @@
         <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="F31">
         <v>2553</v>
@@ -1914,10 +2013,10 @@
         <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F32">
         <v>2520</v>
@@ -1946,10 +2045,10 @@
         <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="F33">
         <v>2498</v>
@@ -1978,10 +2077,10 @@
         <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F34">
         <v>2809</v>
@@ -2010,10 +2109,10 @@
         <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="F35">
         <v>2748</v>
@@ -2042,10 +2141,10 @@
         <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E36" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="F36">
         <v>2646</v>
@@ -2074,10 +2173,10 @@
         <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="F37">
         <v>2715</v>
@@ -2106,10 +2205,10 @@
         <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E38" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="F38">
         <v>2776</v>
@@ -2138,10 +2237,10 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="F39">
         <v>2592</v>
@@ -2170,10 +2269,10 @@
         <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="F40">
         <v>2487</v>
@@ -2202,10 +2301,10 @@
         <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E41" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="F41">
         <v>2445</v>
@@ -2234,10 +2333,10 @@
         <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E42" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="F42">
         <v>2443</v>
@@ -2266,10 +2365,10 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E43" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="F43">
         <v>2450</v>
@@ -2298,10 +2397,10 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E44" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="F44">
         <v>2452</v>
@@ -2330,10 +2429,10 @@
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E45" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="F45">
         <v>2523</v>
@@ -2362,10 +2461,10 @@
         <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E46" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="F46">
         <v>2452</v>
@@ -2394,10 +2493,10 @@
         <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E47" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="F47">
         <v>2735</v>
@@ -2426,10 +2525,10 @@
         <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E48" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="F48">
         <v>2832</v>
@@ -2458,10 +2557,10 @@
         <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E49" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="F49">
         <v>2617</v>
@@ -2490,10 +2589,10 @@
         <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E50" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F50">
         <v>2274</v>
@@ -2522,10 +2621,10 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E51" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="F51">
         <v>3381</v>
@@ -2554,10 +2653,10 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F52">
         <v>2749</v>
@@ -2586,10 +2685,10 @@
         <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E53" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="F53">
         <v>2304</v>
@@ -2618,10 +2717,10 @@
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E54" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="F54">
         <v>2857</v>
@@ -2647,16 +2746,16 @@
         <v>62</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E55" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F55">
-        <v>2938</v>
+        <v>0</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2665,10 +2764,10 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2679,28 +2778,28 @@
         <v>63</v>
       </c>
       <c r="C56">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
+        <v>131</v>
+      </c>
+      <c r="E56" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56">
+        <v>2377</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>221</v>
+      </c>
+      <c r="J56">
         <v>3</v>
-      </c>
-      <c r="D56" t="s">
-        <v>120</v>
-      </c>
-      <c r="E56" t="s">
-        <v>177</v>
-      </c>
-      <c r="F56">
-        <v>3093</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>281</v>
-      </c>
-      <c r="J56">
-        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2711,16 +2810,16 @@
         <v>64</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E57" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="F57">
-        <v>3017</v>
+        <v>2500</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2729,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2743,28 +2842,380 @@
         <v>65</v>
       </c>
       <c r="C58">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>133</v>
+      </c>
+      <c r="E58" t="s">
+        <v>201</v>
+      </c>
+      <c r="F58">
+        <v>2512</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>169</v>
+      </c>
+      <c r="J58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s">
+        <v>134</v>
+      </c>
+      <c r="E59" t="s">
+        <v>202</v>
+      </c>
+      <c r="F59">
+        <v>2512</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>216</v>
+      </c>
+      <c r="J59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60" t="s">
+        <v>203</v>
+      </c>
+      <c r="F60">
+        <v>2531</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>231</v>
+      </c>
+      <c r="J60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61">
+        <v>16</v>
+      </c>
+      <c r="D61" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" t="s">
+        <v>204</v>
+      </c>
+      <c r="F61">
+        <v>2590</v>
+      </c>
+      <c r="G61">
         <v>5</v>
       </c>
-      <c r="D58" t="s">
-        <v>122</v>
-      </c>
-      <c r="E58" t="s">
-        <v>179</v>
-      </c>
-      <c r="F58">
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>229</v>
+      </c>
+      <c r="J61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" t="s">
+        <v>205</v>
+      </c>
+      <c r="F62">
+        <v>2938</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>260</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" t="s">
+        <v>206</v>
+      </c>
+      <c r="F63">
+        <v>3093</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>281</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64">
+        <v>4</v>
+      </c>
+      <c r="D64" t="s">
+        <v>139</v>
+      </c>
+      <c r="E64" t="s">
+        <v>207</v>
+      </c>
+      <c r="F64">
+        <v>3017</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>140</v>
+      </c>
+      <c r="E65" t="s">
+        <v>208</v>
+      </c>
+      <c r="F65">
         <v>2992</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" t="s">
+        <v>209</v>
+      </c>
+      <c r="F66">
+        <v>2835</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>311</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67">
+        <v>7</v>
+      </c>
+      <c r="D67" t="s">
+        <v>142</v>
+      </c>
+      <c r="E67" t="s">
+        <v>210</v>
+      </c>
+      <c r="F67">
+        <v>3039</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>143</v>
+      </c>
+      <c r="E68" t="s">
+        <v>211</v>
+      </c>
+      <c r="F68">
+        <v>2801</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>309</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" t="s">
+        <v>212</v>
+      </c>
+      <c r="F69">
+        <v>2760</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>276</v>
+      </c>
+      <c r="J69">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
